--- a/PSE Calcul complet FATTON.xlsx
+++ b/PSE Calcul complet FATTON.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2ddc44d6d8471646/1. AIQ/PSE/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2041" documentId="8_{9B6B5871-20E1-4B41-9727-41AEF32D48D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A4180FB-B33B-45D6-95D6-E6637622B5DE}"/>
+  <xr:revisionPtr revIDLastSave="2042" documentId="8_{9B6B5871-20E1-4B41-9727-41AEF32D48D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FBEDFC2D-4075-4469-B94F-1341E51AA6EA}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="868" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="868" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="👥 Personnel" sheetId="3" r:id="rId1"/>
@@ -4940,15 +4940,6 @@
     <xf numFmtId="4" fontId="68" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4959,6 +4950,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="33" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="33" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="35" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -26731,28 +26731,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34" ht="23.25" x14ac:dyDescent="0.7">
-      <c r="A1" s="360" t="s">
+      <c r="A1" s="353" t="s">
         <v>139</v>
       </c>
-      <c r="B1" s="361"/>
-      <c r="C1" s="361"/>
-      <c r="D1" s="361"/>
-      <c r="E1" s="361"/>
-      <c r="F1" s="361"/>
-      <c r="G1" s="361"/>
-      <c r="H1" s="361"/>
-      <c r="I1" s="361"/>
-      <c r="J1" s="361"/>
-      <c r="K1" s="361"/>
-      <c r="L1" s="361"/>
-      <c r="M1" s="361"/>
-      <c r="N1" s="361"/>
-      <c r="O1" s="361"/>
-      <c r="P1" s="361"/>
-      <c r="Q1" s="361"/>
-      <c r="R1" s="361"/>
-      <c r="S1" s="361"/>
-      <c r="T1" s="361"/>
+      <c r="B1" s="354"/>
+      <c r="C1" s="354"/>
+      <c r="D1" s="354"/>
+      <c r="E1" s="354"/>
+      <c r="F1" s="354"/>
+      <c r="G1" s="354"/>
+      <c r="H1" s="354"/>
+      <c r="I1" s="354"/>
+      <c r="J1" s="354"/>
+      <c r="K1" s="354"/>
+      <c r="L1" s="354"/>
+      <c r="M1" s="354"/>
+      <c r="N1" s="354"/>
+      <c r="O1" s="354"/>
+      <c r="P1" s="354"/>
+      <c r="Q1" s="354"/>
+      <c r="R1" s="354"/>
+      <c r="S1" s="354"/>
+      <c r="T1" s="354"/>
       <c r="V1" s="283" t="s">
         <v>5</v>
       </c>
@@ -27089,24 +27089,24 @@
       </c>
     </row>
     <row r="7" spans="1:34" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="362" t="s">
+      <c r="A7" s="355" t="s">
         <v>160</v>
       </c>
-      <c r="B7" s="362"/>
-      <c r="C7" s="362"/>
-      <c r="D7" s="362"/>
-      <c r="E7" s="362"/>
-      <c r="F7" s="362"/>
-      <c r="G7" s="362"/>
-      <c r="I7" s="362" t="s">
+      <c r="B7" s="355"/>
+      <c r="C7" s="355"/>
+      <c r="D7" s="355"/>
+      <c r="E7" s="355"/>
+      <c r="F7" s="355"/>
+      <c r="G7" s="355"/>
+      <c r="I7" s="355" t="s">
         <v>161</v>
       </c>
-      <c r="J7" s="362"/>
-      <c r="K7" s="362"/>
-      <c r="L7" s="362"/>
-      <c r="M7" s="362"/>
-      <c r="N7" s="362"/>
-      <c r="O7" s="362"/>
+      <c r="J7" s="355"/>
+      <c r="K7" s="355"/>
+      <c r="L7" s="355"/>
+      <c r="M7" s="355"/>
+      <c r="N7" s="355"/>
+      <c r="O7" s="355"/>
       <c r="V7" s="284" t="str">
         <f>A14</f>
         <v/>
@@ -27661,15 +27661,15 @@
       <c r="AG14" s="284"/>
     </row>
     <row r="15" spans="1:34" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="363" t="s">
+      <c r="A15" s="356" t="s">
         <v>171</v>
       </c>
-      <c r="B15" s="363"/>
-      <c r="C15" s="363"/>
-      <c r="D15" s="363"/>
-      <c r="E15" s="363"/>
-      <c r="F15" s="363"/>
-      <c r="G15" s="363"/>
+      <c r="B15" s="356"/>
+      <c r="C15" s="356"/>
+      <c r="D15" s="356"/>
+      <c r="E15" s="356"/>
+      <c r="F15" s="356"/>
+      <c r="G15" s="356"/>
       <c r="V15" s="284" t="s">
         <v>172</v>
       </c>
@@ -27718,15 +27718,15 @@
       <c r="G16" s="85" t="s">
         <v>166</v>
       </c>
-      <c r="I16" s="363" t="s">
+      <c r="I16" s="356" t="s">
         <v>176</v>
       </c>
-      <c r="J16" s="363"/>
-      <c r="K16" s="363"/>
-      <c r="L16" s="363"/>
-      <c r="M16" s="363"/>
-      <c r="N16" s="363"/>
-      <c r="O16" s="363"/>
+      <c r="J16" s="356"/>
+      <c r="K16" s="356"/>
+      <c r="L16" s="356"/>
+      <c r="M16" s="356"/>
+      <c r="N16" s="356"/>
+      <c r="O16" s="356"/>
       <c r="V16" s="284" t="s">
         <v>177</v>
       </c>
@@ -27941,15 +27941,15 @@
       <c r="AG20" s="284"/>
     </row>
     <row r="21" spans="1:33" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="I21" s="359" t="s">
+      <c r="I21" s="352" t="s">
         <v>182</v>
       </c>
-      <c r="J21" s="359"/>
-      <c r="K21" s="359"/>
-      <c r="L21" s="359"/>
-      <c r="M21" s="359"/>
-      <c r="N21" s="359"/>
-      <c r="O21" s="359"/>
+      <c r="J21" s="352"/>
+      <c r="K21" s="352"/>
+      <c r="L21" s="352"/>
+      <c r="M21" s="352"/>
+      <c r="N21" s="352"/>
+      <c r="O21" s="352"/>
       <c r="V21" s="284"/>
       <c r="W21" s="284"/>
       <c r="X21" s="284"/>
@@ -28138,23 +28138,23 @@
       <c r="G28" s="181"/>
     </row>
     <row r="29" spans="1:33" ht="35.1" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A29" s="358" t="s">
+      <c r="A29" s="351" t="s">
         <v>192</v>
       </c>
-      <c r="B29" s="358"/>
-      <c r="C29" s="358"/>
-      <c r="D29" s="358"/>
-      <c r="E29" s="358"/>
-      <c r="F29" s="358"/>
-      <c r="G29" s="358"/>
-      <c r="H29" s="358"/>
-      <c r="I29" s="358"/>
-      <c r="J29" s="358"/>
-      <c r="K29" s="358"/>
-      <c r="L29" s="358"/>
-      <c r="M29" s="358"/>
-      <c r="N29" s="358"/>
-      <c r="O29" s="358"/>
+      <c r="B29" s="351"/>
+      <c r="C29" s="351"/>
+      <c r="D29" s="351"/>
+      <c r="E29" s="351"/>
+      <c r="F29" s="351"/>
+      <c r="G29" s="351"/>
+      <c r="H29" s="351"/>
+      <c r="I29" s="351"/>
+      <c r="J29" s="351"/>
+      <c r="K29" s="351"/>
+      <c r="L29" s="351"/>
+      <c r="M29" s="351"/>
+      <c r="N29" s="351"/>
+      <c r="O29" s="351"/>
     </row>
     <row r="30" spans="1:33" ht="8.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A30" s="212"/>
@@ -28183,14 +28183,14 @@
       <c r="C31" s="203" t="s">
         <v>195</v>
       </c>
-      <c r="E31" s="355" t="s">
+      <c r="E31" s="361" t="s">
         <v>196</v>
       </c>
-      <c r="F31" s="355"/>
-      <c r="G31" s="355"/>
-      <c r="H31" s="355"/>
-      <c r="I31" s="355"/>
-      <c r="J31" s="355"/>
+      <c r="F31" s="361"/>
+      <c r="G31" s="361"/>
+      <c r="H31" s="361"/>
+      <c r="I31" s="361"/>
+      <c r="J31" s="361"/>
     </row>
     <row r="32" spans="1:33" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A32" s="204" t="s">
@@ -28337,39 +28337,39 @@
       <c r="G38" s="181"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="E39" s="356" t="s">
+      <c r="E39" s="362" t="s">
         <v>212</v>
       </c>
-      <c r="F39" s="357"/>
+      <c r="F39" s="363"/>
       <c r="G39" s="230" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="E40" s="351" t="s">
+      <c r="E40" s="357" t="s">
         <v>214</v>
       </c>
-      <c r="F40" s="352"/>
+      <c r="F40" s="358"/>
       <c r="G40" s="231">
         <f>J4</f>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="E41" s="351" t="s">
+      <c r="E41" s="357" t="s">
         <v>215</v>
       </c>
-      <c r="F41" s="352"/>
+      <c r="F41" s="358"/>
       <c r="G41" s="231">
         <f>K4</f>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="E42" s="353" t="s">
+      <c r="E42" s="359" t="s">
         <v>216</v>
       </c>
-      <c r="F42" s="354"/>
+      <c r="F42" s="360"/>
       <c r="G42" s="232">
         <f>L4</f>
         <v>0</v>
@@ -28394,6 +28394,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="E31:J31"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="E40:F40"/>
     <mergeCell ref="A29:O29"/>
     <mergeCell ref="I21:O21"/>
     <mergeCell ref="A1:T1"/>
@@ -28401,11 +28406,6 @@
     <mergeCell ref="I7:O7"/>
     <mergeCell ref="A15:G15"/>
     <mergeCell ref="I16:O16"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="E31:J31"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="E40:F40"/>
   </mergeCells>
   <conditionalFormatting sqref="C9:C11">
     <cfRule type="cellIs" dxfId="6" priority="1" operator="greaterThan">
@@ -30043,25 +30043,25 @@
       <c r="A1" s="370" t="s">
         <v>279</v>
       </c>
-      <c r="B1" s="361"/>
-      <c r="C1" s="361"/>
-      <c r="D1" s="361"/>
-      <c r="E1" s="361"/>
-      <c r="F1" s="361"/>
-      <c r="G1" s="361"/>
-      <c r="H1" s="361"/>
-      <c r="I1" s="361"/>
-      <c r="J1" s="361"/>
-      <c r="K1" s="361"/>
-      <c r="L1" s="361"/>
-      <c r="M1" s="361"/>
-      <c r="N1" s="361"/>
-      <c r="O1" s="361"/>
-      <c r="P1" s="361"/>
-      <c r="Q1" s="361"/>
-      <c r="R1" s="361"/>
-      <c r="S1" s="361"/>
-      <c r="T1" s="361"/>
+      <c r="B1" s="354"/>
+      <c r="C1" s="354"/>
+      <c r="D1" s="354"/>
+      <c r="E1" s="354"/>
+      <c r="F1" s="354"/>
+      <c r="G1" s="354"/>
+      <c r="H1" s="354"/>
+      <c r="I1" s="354"/>
+      <c r="J1" s="354"/>
+      <c r="K1" s="354"/>
+      <c r="L1" s="354"/>
+      <c r="M1" s="354"/>
+      <c r="N1" s="354"/>
+      <c r="O1" s="354"/>
+      <c r="P1" s="354"/>
+      <c r="Q1" s="354"/>
+      <c r="R1" s="354"/>
+      <c r="S1" s="354"/>
+      <c r="T1" s="354"/>
     </row>
     <row r="3" spans="1:20" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A3" s="322" t="s">
@@ -32961,13 +32961,13 @@
       <c r="A40" s="369" t="s">
         <v>285</v>
       </c>
-      <c r="B40" s="361"/>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
-      <c r="G40" s="361"/>
-      <c r="H40" s="361"/>
+      <c r="B40" s="354"/>
+      <c r="C40" s="354"/>
+      <c r="D40" s="354"/>
+      <c r="E40" s="354"/>
+      <c r="F40" s="354"/>
+      <c r="G40" s="354"/>
+      <c r="H40" s="354"/>
       <c r="I40" s="350">
         <f>SUM(TPersonnel[INDEM LÉGALE])</f>
         <v>0</v>
@@ -33036,18 +33036,18 @@
       <c r="A1" s="370" t="s">
         <v>286</v>
       </c>
-      <c r="B1" s="361"/>
-      <c r="C1" s="361"/>
-      <c r="D1" s="361"/>
-      <c r="E1" s="361"/>
-      <c r="F1" s="361"/>
+      <c r="B1" s="354"/>
+      <c r="C1" s="354"/>
+      <c r="D1" s="354"/>
+      <c r="E1" s="354"/>
+      <c r="F1" s="354"/>
     </row>
     <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A4" s="371" t="s">
         <v>287</v>
       </c>
-      <c r="B4" s="361"/>
-      <c r="C4" s="361"/>
+      <c r="B4" s="354"/>
+      <c r="C4" s="354"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B6" s="1" t="s">
@@ -33097,8 +33097,8 @@
       <c r="A13" s="371" t="s">
         <v>292</v>
       </c>
-      <c r="B13" s="361"/>
-      <c r="C13" s="361"/>
+      <c r="B13" s="354"/>
+      <c r="C13" s="354"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B15" s="1" t="s">
@@ -33157,8 +33157,8 @@
       <c r="A23" s="372" t="s">
         <v>297</v>
       </c>
-      <c r="B23" s="361"/>
-      <c r="C23" s="361"/>
+      <c r="B23" s="354"/>
+      <c r="C23" s="354"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B25" s="1" t="s">
@@ -33257,14 +33257,14 @@
       <c r="A1" s="370" t="s">
         <v>304</v>
       </c>
-      <c r="B1" s="361"/>
-      <c r="C1" s="361"/>
-      <c r="D1" s="361"/>
-      <c r="E1" s="361"/>
-      <c r="F1" s="361"/>
-      <c r="G1" s="361"/>
-      <c r="H1" s="361"/>
-      <c r="I1" s="361"/>
+      <c r="B1" s="354"/>
+      <c r="C1" s="354"/>
+      <c r="D1" s="354"/>
+      <c r="E1" s="354"/>
+      <c r="F1" s="354"/>
+      <c r="G1" s="354"/>
+      <c r="H1" s="354"/>
+      <c r="I1" s="354"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="324" t="s">
@@ -36594,9 +36594,9 @@
       <c r="A1" s="370" t="s">
         <v>388</v>
       </c>
-      <c r="B1" s="361"/>
-      <c r="C1" s="361"/>
-      <c r="D1" s="361"/>
+      <c r="B1" s="354"/>
+      <c r="C1" s="354"/>
+      <c r="D1" s="354"/>
       <c r="J1" s="182" t="s">
         <v>389</v>
       </c>
